--- a/artfynd/A 1650-2022 artfynd.xlsx
+++ b/artfynd/A 1650-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1650-2022 artfynd.xlsx
+++ b/artfynd/A 1650-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98581862</v>
+        <v>99361224</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Malghult naturskog, Sm</t>
+          <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570375.8486136473</v>
+        <v>570378</v>
       </c>
       <c r="R2" t="n">
-        <v>6362970.204520325</v>
+        <v>6362961</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +768,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98581856</v>
+        <v>99361622</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,42 +791,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Malghult naturskog, Sm</t>
+          <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570375.8486136473</v>
+        <v>570261</v>
       </c>
       <c r="R3" t="n">
-        <v>6362970.204520325</v>
+        <v>6363004</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -917,65 +877,59 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98581847</v>
+        <v>99361662</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Malghult naturskog, Sm</t>
+          <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570375.8486136473</v>
+        <v>570274</v>
       </c>
       <c r="R4" t="n">
-        <v>6362970.204520325</v>
+        <v>6363023</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,56 +970,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99362153</v>
+        <v>99363195</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,16 +1023,21 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570159.2187929787</v>
+        <v>570336</v>
       </c>
       <c r="R5" t="n">
-        <v>6363040.837851411</v>
+        <v>6363052</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,19 +1067,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,68 +1084,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99361923</v>
+        <v>99360680</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570196.1143027376</v>
+        <v>570415</v>
       </c>
       <c r="R6" t="n">
-        <v>6363030.156180491</v>
+        <v>6362947</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1242,19 +1171,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,52 +1200,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99362096</v>
+        <v>99361144</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570167.1542084841</v>
+        <v>570409</v>
       </c>
       <c r="R7" t="n">
-        <v>6363018.882109104</v>
+        <v>6362939</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1356,24 +1275,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>15-tal plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,56 +1304,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99362058</v>
+        <v>98581873</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oskarshamn, Sm</t>
+          <t>Malghult naturskog, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570160.2395248389</v>
+        <v>570376</v>
       </c>
       <c r="R8" t="n">
-        <v>6363012.836216123</v>
+        <v>6362970</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1476,22 +1381,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,63 +1406,59 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99361713</v>
+        <v>99361749</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570269.0697296733</v>
+        <v>570269</v>
       </c>
       <c r="R9" t="n">
-        <v>6363026.021979663</v>
+        <v>6363026</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1597,19 +1488,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,52 +1517,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99362061</v>
+        <v>99362863</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570169.2946089675</v>
+        <v>570245</v>
       </c>
       <c r="R10" t="n">
-        <v>6363019.996530878</v>
+        <v>6363063</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1711,24 +1592,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>15-tal plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,15 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99361500</v>
+        <v>98581862</v>
       </c>
       <c r="B11" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,24 +1649,33 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Oskarshamn, Sm</t>
+          <t>Malghult naturskog, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570288.3978899046</v>
+        <v>570376</v>
       </c>
       <c r="R11" t="n">
-        <v>6363032.281583217</v>
+        <v>6362970</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1832,27 +1702,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Sångläte</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,27 +1722,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99361622</v>
+        <v>99361500</v>
       </c>
       <c r="B12" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,41 +1745,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570260.2742027181</v>
+        <v>570288</v>
       </c>
       <c r="R12" t="n">
-        <v>6363003.778595983</v>
+        <v>6363032</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1959,19 +1809,14 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Sångläte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,27 +1831,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99361125</v>
+        <v>98581847</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,21 +1873,23 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oskarshamn, Sm</t>
+          <t>Malghult naturskog, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570409.3292678229</v>
+        <v>570376</v>
       </c>
       <c r="R13" t="n">
-        <v>6362938.450897109</v>
+        <v>6362970</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2074,22 +1916,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,33 +1930,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99361651</v>
+        <v>99360840</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +1979,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2162,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570274.5225709323</v>
+        <v>570419</v>
       </c>
       <c r="R14" t="n">
-        <v>6363022.882780144</v>
+        <v>6362933</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2195,19 +2023,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,65 +2040,63 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99361224</v>
+        <v>99361125</v>
       </c>
       <c r="B15" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570378.1838419444</v>
+        <v>570409</v>
       </c>
       <c r="R15" t="n">
-        <v>6362960.006796781</v>
+        <v>6362939</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2310,24 +2126,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,57 +2155,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99361662</v>
+        <v>99361651</v>
       </c>
       <c r="B16" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oskarshamn, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570274.5225709323</v>
+        <v>570274</v>
       </c>
       <c r="R16" t="n">
-        <v>6363022.882780144</v>
+        <v>6363023</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2434,19 +2229,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,15 +2258,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99362020</v>
+        <v>99361713</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2286,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2515,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570169.1465867979</v>
+        <v>570269</v>
       </c>
       <c r="R17" t="n">
-        <v>6363028.615275881</v>
+        <v>6363026</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2548,24 +2332,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>20-tal plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,15 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99360840</v>
+        <v>99361923</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,7 +2391,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2638,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570418.0671796014</v>
+        <v>570197</v>
       </c>
       <c r="R18" t="n">
-        <v>6362932.674206346</v>
+        <v>6363030</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2671,19 +2435,9 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-03-22</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2710,37 +2464,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99362568</v>
+        <v>99362020</v>
       </c>
       <c r="B19" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2752,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570171.2684782776</v>
+        <v>570169</v>
       </c>
       <c r="R19" t="n">
-        <v>6363030.807037758</v>
+        <v>6363029</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2785,19 +2534,14 @@
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-03-22</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>20-tal plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,6 +2565,724 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>99362058</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oskarshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>570161</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6363013</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>99362061</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oskarshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570169</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6363020</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>15-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>99362096</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oskarshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570168</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6363019</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>99362153</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oskarshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570159</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6363040</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>98581856</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Malghult naturskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570376</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6362970</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-02-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-02-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>99362568</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oskarshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570171</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6363031</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>99363079</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oskarshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570330</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6363063</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1650-2022 artfynd.xlsx
+++ b/artfynd/A 1650-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99363195</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99360680</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361144</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98581873</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361749</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99362863</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98581862</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1840,6 +1895,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361500</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98581847</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99360840</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361125</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2255,6 +2330,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361651</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361713</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,6 +2546,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99361923</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2565,6 +2655,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99362020</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99362058</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99362061</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2876,6 +2981,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99362096</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2979,6 +3089,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99362153</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3085,6 +3200,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98581856</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3184,6 +3304,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99362568</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3283,8 +3408,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99363079</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>